--- a/templates/forms/LTCI_Certification_Withdrawal_Request.xlsx
+++ b/templates/forms/LTCI_Certification_Withdrawal_Request.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C720E72-A314-46FA-A074-E58A417A60F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6440C1-2280-4B13-8509-2ACE64870BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A85BED77-065D-431F-A895-4760ACDC02F2}"/>
   </bookViews>
@@ -766,7 +766,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -837,6 +837,75 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -845,6 +914,37 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -855,13 +955,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -870,40 +964,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -913,84 +977,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed" textRotation="255"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1405,23 +1408,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
     </row>
     <row r="2" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="3" spans="1:15" ht="18.75" x14ac:dyDescent="0.15">
@@ -1434,126 +1437,126 @@
     </row>
     <row r="5" spans="1:15" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A5" s="3"/>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
     </row>
     <row r="6" spans="1:15" ht="18.75" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="33"/>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="65"/>
     </row>
     <row r="7" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="58" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="32"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="46"/>
       <c r="M8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="30"/>
-      <c r="O8" s="41"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="67"/>
     </row>
     <row r="9" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="72"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="46" t="s">
+      <c r="C9" s="71"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="42"/>
-      <c r="O9" s="43"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="68"/>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="72"/>
-      <c r="B10" s="52" t="s">
+      <c r="A10" s="59"/>
+      <c r="B10" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="45"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="69"/>
+      <c r="O10" s="70"/>
     </row>
     <row r="11" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="72"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="57"/>
-      <c r="K11" s="57"/>
-      <c r="L11" s="58"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="56"/>
       <c r="M11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="N11" s="30"/>
-      <c r="O11" s="32"/>
+      <c r="N11" s="45"/>
+      <c r="O11" s="46"/>
     </row>
     <row r="12" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="72"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="59"/>
+      <c r="B12" s="33" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -1562,36 +1565,36 @@
       <c r="D12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
       <c r="J12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O12" s="10"/>
     </row>
     <row r="13" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="72"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="26"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="49"/>
     </row>
     <row r="14" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="73"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="60"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
@@ -1605,8 +1608,8 @@
       <c r="M14" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="39"/>
-      <c r="O14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
     </row>
     <row r="15" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="12"/>
@@ -1626,46 +1629,46 @@
       <c r="O15" s="15"/>
     </row>
     <row r="16" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="74"/>
-      <c r="M16" s="74"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="75"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="76"/>
     </row>
     <row r="17" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="66"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="78"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="79"/>
     </row>
     <row r="18" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="66"/>
-      <c r="B18" s="46" t="s">
+      <c r="A18" s="31"/>
+      <c r="B18" s="33" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="9" t="s">
@@ -1674,36 +1677,36 @@
       <c r="D18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
       <c r="J18" s="1" t="s">
         <v>21</v>
       </c>
       <c r="O18" s="10"/>
     </row>
     <row r="19" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="66"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="26"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="49"/>
     </row>
     <row r="20" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="48"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
@@ -1717,28 +1720,28 @@
       <c r="M20" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="39"/>
-      <c r="O20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="41"/>
     </row>
     <row r="21" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="22" spans="1:15" ht="78.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="29"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="63"/>
     </row>
     <row r="23" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="24" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
@@ -1759,23 +1762,23 @@
       <c r="O24" s="19"/>
     </row>
     <row r="25" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="37"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="43"/>
+      <c r="M25" s="43"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="44"/>
     </row>
     <row r="26" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="20"/>
@@ -1786,43 +1789,43 @@
       <c r="B27" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="59" t="s">
+      <c r="G27" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="61"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="26"/>
     </row>
     <row r="28" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="20"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="62"/>
-      <c r="N28" s="62"/>
-      <c r="O28" s="63"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="28"/>
     </row>
     <row r="29" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="20"/>
-      <c r="G29" s="64" t="s">
+      <c r="G29" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="60"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="61"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="26"/>
     </row>
     <row r="30" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="22"/>
@@ -1831,18 +1834,35 @@
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="62"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="62"/>
-      <c r="O30" s="63"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="N9:O10"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="A8:A14"/>
+    <mergeCell ref="C19:O19"/>
+    <mergeCell ref="B22:O22"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="B5:O6"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="E12:I12"/>
+    <mergeCell ref="C13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:L11"/>
+    <mergeCell ref="M9:M10"/>
     <mergeCell ref="G27:O28"/>
     <mergeCell ref="G29:O30"/>
     <mergeCell ref="A16:A20"/>
@@ -1852,23 +1872,6 @@
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="N20:O20"/>
     <mergeCell ref="A25:O25"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="E12:I12"/>
-    <mergeCell ref="C13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:L11"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="A8:A14"/>
-    <mergeCell ref="C19:O19"/>
-    <mergeCell ref="B22:O22"/>
-    <mergeCell ref="C8:L8"/>
-    <mergeCell ref="B5:O6"/>
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="N9:O10"/>
-    <mergeCell ref="C9:L9"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
